--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260826.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260826.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>75,207</t>
+          <t>75,407</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.94%</t>
+          <t>11.05%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>30,996</t>
+          <t>31,196</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.21%</t>
+          <t>10.39%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>86,925</t>
+          <t>87,425</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.90%</t>
+          <t>8.06%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>34,155</t>
+          <t>34,355</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.33%</t>
+          <t>7.41%</t>
         </is>
       </c>
     </row>
@@ -699,12 +699,12 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>187,756</t>
+          <t>189,056</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.62%</t>
+          <t>5.56%</t>
         </is>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>99,791</t>
+          <t>100,491</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.31%</t>
+          <t>4.28%</t>
         </is>
       </c>
     </row>
@@ -743,12 +743,12 @@
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>47,095</t>
+          <t>47,395</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.64%</t>
+          <t>3.61%</t>
         </is>
       </c>
     </row>
@@ -765,56 +765,56 @@
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>108,266</t>
+          <t>108,966</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.46%</t>
+          <t>3.42%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>HUBB US</t>
+          <t>NVT US</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>安柏</t>
+          <t>nVent Electric PLC</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>18,679</t>
+          <t>57,059</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.08%</t>
+          <t>3.10%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NVT US</t>
+          <t>HUBB US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>nVent Electric PLC</t>
+          <t>安柏</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>56,759</t>
+          <t>18,679</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.06%</t>
+          <t>3.08%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>112,583</t>
+          <t>113,383</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.68%</t>
+          <t>2.65%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>52,127</t>
+          <t>52,527</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.28%</t>
+          <t>2.26%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>21,631</t>
+          <t>21,731</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.14%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>131,101</t>
+          <t>132,001</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.07%</t>
+          <t>2.05%</t>
         </is>
       </c>
     </row>
@@ -919,12 +919,12 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,404</t>
+          <t>23,504</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.72%</t>
+          <t>1.69%</t>
         </is>
       </c>
     </row>
@@ -941,7 +941,7 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>59,903</t>
+          <t>60,303</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>35,380</t>
+          <t>35,580</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.35%</t>
+          <t>1.34%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>49,210</t>
+          <t>49,610</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>47,836</t>
+          <t>48,136</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>74,101</t>
+          <t>74,501</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.22%</t>
         </is>
       </c>
     </row>
@@ -1051,12 +1051,12 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>48,160</t>
+          <t>48,460</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.22%</t>
+          <t>1.21%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>91,463</t>
+          <t>92,063</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>31,310</t>
+          <t>31,410</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>29,245</t>
+          <t>29,445</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
@@ -1139,7 +1139,7 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>21,458</t>
+          <t>21,558</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>45,227</t>
+          <t>45,527</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>26,469</t>
+          <t>26,669</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1205,7 +1205,7 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>19,909</t>
+          <t>20,009</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1249,12 +1249,12 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>140,345</t>
+          <t>141,345</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.90%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>72,174</t>
+          <t>72,674</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.89%</t>
         </is>
       </c>
     </row>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.85%</t>
+          <t>0.86%</t>
         </is>
       </c>
     </row>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>29,114</t>
+          <t>29,314</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>0.82%</t>
+          <t>0.81%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.75%</t>
         </is>
       </c>
     </row>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>29,491</t>
+          <t>29,691</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>24,781</t>
+          <t>24,881</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>41,783</t>
+          <t>42,083</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>90,902</t>
+          <t>91,502</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.48%</t>
+          <t>0.47%</t>
         </is>
       </c>
     </row>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>0.37%</t>
+          <t>0.39%</t>
         </is>
       </c>
     </row>
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>22,619</t>
+          <t>22,719</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.30%</t>
+          <t>0.31%</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>17,753</t>
+          <t>17,853</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>36,761</t>
+          <t>37,061</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>131,369,081</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
